--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -723,25 +723,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>15.38</v>
+        <v>3.85</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1564,25 +1564,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>15.38</v>
+        <v>3.85</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -950,22 +950,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>8.57</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -982,22 +985,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>52.38</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>47.62</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1014,22 +1020,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>64.86</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>35.14</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1046,22 +1055,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1078,22 +1090,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>6.45</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1110,22 +1125,25 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>96.67</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>3.33</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1142,22 +1160,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>3.85</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1174,22 +1195,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1206,22 +1230,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1238,22 +1265,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.1</v>
       </c>
       <c r="J11">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1270,22 +1300,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9.1</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1354,19 +1387,19 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>97.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>2.86</v>
+        <v>5.71</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1401,7 +1434,7 @@
         <v>47.62</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -1436,7 +1469,7 @@
         <v>32.43</v>
       </c>
       <c r="I4" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
         <v>12</v>
@@ -1471,7 +1504,7 @@
         <v>3.13</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1494,19 +1527,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>93.55</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1529,19 +1562,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H7" s="1">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1576,7 +1609,7 @@
         <v>3.85</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1611,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1634,19 +1667,19 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>94.73999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H10" s="1">
-        <v>5.26</v>
+        <v>21.05</v>
       </c>
       <c r="I10" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1669,19 +1702,19 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>97.06</v>
+        <v>94.12</v>
       </c>
       <c r="H11" s="1">
-        <v>2.94</v>
+        <v>5.88</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1716,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -1055,25 +1055,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H5" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>15.63</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1492,19 +1492,19 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>96.88</v>
+        <v>93.75</v>
       </c>
       <c r="H5" s="1">
-        <v>3.13</v>
+        <v>6.25</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>1</v>

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -950,25 +950,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="I2" s="2">
         <v>7.8</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>5.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="3" spans="1:11">

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -528,10 +528,10 @@
         <v>7.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -548,25 +548,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>47.62</v>
+        <v>4.76</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -583,25 +583,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H4" s="1">
-        <v>32.43</v>
+        <v>18.92</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>32.43</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -630,13 +630,13 @@
         <v>3.13</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -962,13 +962,13 @@
         <v>5.71</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -985,25 +985,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>52.38</v>
+        <v>90.48</v>
       </c>
       <c r="H3" s="1">
-        <v>47.62</v>
+        <v>9.52</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>47.62</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1020,25 +1020,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>64.86</v>
+        <v>81.08</v>
       </c>
       <c r="H4" s="1">
-        <v>35.14</v>
+        <v>18.92</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>35.14</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1055,25 +1055,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H5" s="1">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1399,13 +1399,13 @@
         <v>5.71</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1422,25 +1422,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>47.62</v>
+        <v>4.76</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1457,25 +1457,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H4" s="1">
-        <v>32.43</v>
+        <v>18.92</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>32.43</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1492,25 +1492,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H5" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -1387,19 +1387,19 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1422,19 +1422,19 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1457,19 +1457,19 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>81.08</v>
+        <v>94.59</v>
       </c>
       <c r="H4" s="1">
-        <v>18.92</v>
+        <v>5.41</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J4">
         <v>1</v>

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -1667,16 +1667,16 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H10" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I10" s="2">
         <v>7.8</v>
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -1527,16 +1527,16 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>8.6</v>
@@ -1562,19 +1562,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>96.67</v>
+        <v>93.33</v>
       </c>
       <c r="H7" s="1">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1597,19 +1597,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1702,19 +1702,19 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>5.88</v>
+        <v>11.76</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>1</v>

--- a/academias/Ciencias Sociales - Estadisticos 20221.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20221.xlsx
@@ -598,10 +598,10 @@
         <v>7.3</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -840,13 +840,13 @@
         <v>2.94</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -985,25 +985,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1032,13 +1032,13 @@
         <v>18.92</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1280,10 +1280,10 @@
         <v>9.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1422,19 +1422,19 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1469,13 +1469,13 @@
         <v>5.41</v>
       </c>
       <c r="I4" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1714,13 +1714,13 @@
         <v>11.76</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
